--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbMonthReportDetailProd001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbMonthReportDetailProd001.xlsx
@@ -120,6 +120,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="180" formatCode="#,##0.000000_ "/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -186,11 +189,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -496,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="9" style="1" customWidth="1"/>
@@ -512,23 +517,24 @@
     <col min="14" max="14" width="15.08984375" style="1" customWidth="1"/>
     <col min="15" max="15" width="15.08984375" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.90625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="13.08984375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.90625" style="5" customWidth="1"/>
+    <col min="18" max="18" width="13.08984375" style="5" customWidth="1"/>
     <col min="19" max="19" width="12.1796875" style="1" customWidth="1"/>
     <col min="20" max="20" width="12.6328125" style="1" customWidth="1"/>
-    <col min="21" max="22" width="8.7265625" style="1"/>
-    <col min="23" max="23" width="18.08984375" style="1" customWidth="1"/>
-    <col min="24" max="24" width="17.6328125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="13" style="1" customWidth="1"/>
-    <col min="26" max="26" width="12.81640625" style="1" customWidth="1"/>
-    <col min="27" max="28" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13" style="1" customWidth="1"/>
-    <col min="33" max="33" width="16.54296875" style="1" customWidth="1"/>
-    <col min="34" max="16384" width="8.7265625" style="1"/>
+    <col min="21" max="22" width="8.7265625" style="5"/>
+    <col min="23" max="23" width="18.08984375" style="5" customWidth="1"/>
+    <col min="24" max="24" width="17.6328125" style="5" customWidth="1"/>
+    <col min="25" max="25" width="13" style="5" customWidth="1"/>
+    <col min="26" max="26" width="12.81640625" style="5" customWidth="1"/>
+    <col min="27" max="28" width="20" style="5" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="13.54296875" style="5" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13" style="5" customWidth="1"/>
+    <col min="33" max="33" width="16.54296875" style="5" customWidth="1"/>
+    <col min="34" max="34" width="8.7265625" style="5"/>
+    <col min="35" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -577,10 +583,10 @@
       <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="3" t="s">
@@ -589,45 +595,46 @@
       <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AA1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AB1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AE1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AG1" s="4" t="s">
         <v>32</v>
       </c>
+      <c r="AH1" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbMonthReportDetailProd001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbMonthReportDetailProd001.xlsx
@@ -8,13 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="G06产品端明细台账" sheetId="5" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
   <si>
     <t>产品代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -114,6 +115,207 @@
   </si>
   <si>
     <t>金融机构资产管理产品余额</t>
+  </si>
+  <si>
+    <t>#{dtoList.prodid}</t>
+  </si>
+  <si>
+    <t>#{dtoList.prodName}</t>
+  </si>
+  <si>
+    <t>#{dtoList.vdateStr}</t>
+  </si>
+  <si>
+    <t>#{dtoList.mdateStr}</t>
+  </si>
+  <si>
+    <t>#{dtoList.raiseTypeStr}</t>
+  </si>
+  <si>
+    <t>#{dtoList.ivstorientationStr}</t>
+  </si>
+  <si>
+    <t>#{dtoList.ccyStr}</t>
+  </si>
+  <si>
+    <t>#{dtoList.operateModeStr}</t>
+  </si>
+  <si>
+    <t>#{dtoList.opentypeStr}</t>
+  </si>
+  <si>
+    <t>#{dtoList.term}</t>
+  </si>
+  <si>
+    <t>#{dtoList.termtypeStr}</t>
+  </si>
+  <si>
+    <t>#{dtoList.isTransferStr}</t>
+  </si>
+  <si>
+    <t>#{dtoList.isBreakevenStr}</t>
+  </si>
+  <si>
+    <t>#{dtoList.isYllccpStr}</t>
+  </si>
+  <si>
+    <t>#{dtoList.excFinSectorStr}</t>
+  </si>
+  <si>
+    <t>#{dtoList.isFhxgcpStr}</t>
+  </si>
+  <si>
+    <t>#{dtoList.dirtyamtsumStr}</t>
+  </si>
+  <si>
+    <t>#{dtoList.cleanamtsumStr}</t>
+  </si>
+  <si>
+    <t>#{dtoList.isThisTremStr}</t>
+  </si>
+  <si>
+    <t>#{dtoList.isEndTremStr}</t>
+  </si>
+  <si>
+    <t>#{dtoList.endamtsumOth}</t>
+  </si>
+  <si>
+    <t>#{dtoList.payamtsum}</t>
+  </si>
+  <si>
+    <t>#{dtoList.customeramt}</t>
+  </si>
+  <si>
+    <t>#{dtoList.bankamt}</t>
+  </si>
+  <si>
+    <t>#{dtoList.ordIdentified01}</t>
+  </si>
+  <si>
+    <t>#{dtoList.ordIdentified02}</t>
+  </si>
+  <si>
+    <t>#{dtoList.ordIdentified03}</t>
+  </si>
+  <si>
+    <t>#{dtoList.ordIdentified04}</t>
+  </si>
+  <si>
+    <t>#{dtoList.ordIdentified05}</t>
+  </si>
+  <si>
+    <t>#{dtoList.ordIdentified06}</t>
+  </si>
+  <si>
+    <t>#{dtoList.ordIdentified07}</t>
+  </si>
+  <si>
+    <t>#{dtoList.ordIdentified08}</t>
+  </si>
+  <si>
+    <t>#{dtoList.ordIdentified09}</t>
+  </si>
+  <si>
+    <t>#{keyList.prodid}</t>
+  </si>
+  <si>
+    <t>#{keyList.prodName}</t>
+  </si>
+  <si>
+    <t>#{keyList.vdateStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.mdateStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.raiseTypeStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.ivstorientationStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.ccyStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.operateModeStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.opentypeStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.term}</t>
+  </si>
+  <si>
+    <t>#{keyList.termtypeStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.isTransferStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.isBreakevenStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.isYllccpStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.excFinSectorStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.isFhxgcpStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.isThisTremStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.isEndTremStr}</t>
+  </si>
+  <si>
+    <t>#{keyList.endamtsumOthDv}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#{keyList.payamtsumDv}</t>
+  </si>
+  <si>
+    <t>#{keyList.customeramtDv}</t>
+  </si>
+  <si>
+    <t>#{keyList.bankamtDv}</t>
+  </si>
+  <si>
+    <t>#{keyList.ordIdentified01Dv}</t>
+  </si>
+  <si>
+    <t>#{keyList.ordIdentified02Dv}</t>
+  </si>
+  <si>
+    <t>#{keyList.ordIdentified03Dv}</t>
+  </si>
+  <si>
+    <t>#{keyList.ordIdentified04Dv}</t>
+  </si>
+  <si>
+    <t>#{keyList.ordIdentified05Dv}</t>
+  </si>
+  <si>
+    <t>#{keyList.ordIdentified06Dv}</t>
+  </si>
+  <si>
+    <t>#{keyList.ordIdentified07Dv}</t>
+  </si>
+  <si>
+    <t>#{keyList.ordIdentified08Dv}</t>
+  </si>
+  <si>
+    <t>#{keyList.ordIdentified09Dv}</t>
+  </si>
+  <si>
+    <t>#{keyList.dirtyamtsumDv}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#{keyList.cleanamtsumDv}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -123,26 +325,28 @@
   <numFmts count="1">
     <numFmt numFmtId="180" formatCode="#,##0.000000_ "/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -187,15 +391,16 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="180" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -501,10 +706,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AH2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="9" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7265625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="9" style="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1" customWidth="1"/>
     <col min="7" max="7" width="12.6328125" style="1" customWidth="1"/>
@@ -636,9 +842,290 @@
       </c>
       <c r="AH1" s="4"/>
     </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N2" t="s">
+        <v>79</v>
+      </c>
+      <c r="O2" t="s">
+        <v>80</v>
+      </c>
+      <c r="P2" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="S2" t="s">
+        <v>82</v>
+      </c>
+      <c r="T2" t="s">
+        <v>83</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="X2" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y2" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA2" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB2" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC2" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD2" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE2" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="AF2" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="AG2" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="AH2" s="1"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:A34"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="31.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbMonthReportDetailProd001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbMonthReportDetailProd001.xlsx
@@ -323,7 +323,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="180" formatCode="#,##0.000000_ "/>
+    <numFmt numFmtId="176" formatCode="#,##0.000000_ "/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -393,14 +393,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -843,103 +842,103 @@
       <c r="AH1" s="4"/>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="Q2" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="R2" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="S2" t="s">
+      <c r="S2" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="T2" t="s">
+      <c r="T2" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="U2" s="6" t="s">
+      <c r="U2" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="V2" s="6" t="s">
+      <c r="V2" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="W2" s="6" t="s">
+      <c r="W2" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="X2" s="6" t="s">
+      <c r="X2" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="Y2" s="6" t="s">
+      <c r="Y2" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="Z2" s="6" t="s">
+      <c r="Z2" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="AA2" s="6" t="s">
+      <c r="AA2" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="AB2" s="6" t="s">
+      <c r="AB2" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="AC2" s="6" t="s">
+      <c r="AC2" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="AD2" s="6" t="s">
+      <c r="AD2" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="AE2" s="6" t="s">
+      <c r="AE2" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="AF2" s="6" t="s">
+      <c r="AF2" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="AG2" s="6" t="s">
+      <c r="AG2" s="5" t="s">
         <v>96</v>
       </c>
       <c r="AH2" s="1"/>
